--- a/data/trans_dic/IP26C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,86</t>
+          <t>0,45; 3,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,89</t>
+          <t>0,45; 4,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 13,89</t>
+          <t>3,83; 14,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,82</t>
+          <t>1,45; 7,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,1</t>
+          <t>2,54; 10,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,49</t>
+          <t>1,19; 4,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,94</t>
+          <t>0,5; 3,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,13</t>
+          <t>3,9; 10,09</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,05</t>
+          <t>2,74; 7,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,19</t>
+          <t>3,22; 8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,59</t>
+          <t>3,17; 8,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,78</t>
+          <t>5,02; 11,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,11</t>
+          <t>3,2; 7,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,0</t>
+          <t>3,24; 7,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,15</t>
+          <t>4,09; 8,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,09</t>
+          <t>5,27; 12,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,49</t>
+          <t>3,47; 6,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,12</t>
+          <t>3,87; 7,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,84</t>
+          <t>4,3; 7,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,67</t>
+          <t>5,86; 10,83</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 17,23</t>
+          <t>7,98; 16,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 17,18</t>
+          <t>8,42; 16,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 17,56</t>
+          <t>9,55; 17,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,66</t>
+          <t>6,81; 14,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 13,3</t>
+          <t>5,5; 13,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,13</t>
+          <t>8,53; 16,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 16,59</t>
+          <t>8,52; 16,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 20,5</t>
+          <t>11,12; 20,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 13,72</t>
+          <t>7,61; 13,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 15,57</t>
+          <t>9,45; 15,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 15,56</t>
+          <t>9,93; 15,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 16,39</t>
+          <t>10,44; 16,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,24; 31,54</t>
+          <t>21,23; 31,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 29,05</t>
+          <t>18,26; 29,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 20,53</t>
+          <t>11,86; 20,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,45</t>
+          <t>5,87; 12,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,18; 24,97</t>
+          <t>16,55; 25,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 29,78</t>
+          <t>19,58; 29,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 22,01</t>
+          <t>12,65; 22,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 13,87</t>
+          <t>7,35; 14,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 26,51</t>
+          <t>19,86; 26,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,72; 27,43</t>
+          <t>20,2; 27,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 19,55</t>
+          <t>13,27; 20,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,42</t>
+          <t>7,46; 12,42</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,84</t>
+          <t>9,61; 13,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,34</t>
+          <t>8,8; 12,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,28</t>
+          <t>7,62; 11,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,95</t>
+          <t>7,18; 11,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,22</t>
+          <t>7,83; 11,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,99</t>
+          <t>9,13; 12,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,15</t>
+          <t>7,65; 11,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,95</t>
+          <t>8,86; 12,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,82</t>
+          <t>9,07; 11,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 12,07</t>
+          <t>9,28; 12,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,68</t>
+          <t>8,15; 10,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,56</t>
+          <t>8,72; 11,66</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2349</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4415</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7684</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4448</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>648; 5521</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>566; 5436</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2200; 8383</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2049; 9965</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4398</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1550; 6657</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4395</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3390; 12058</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1229; 7359</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4624; 11965</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11595</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12696</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11610</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12262</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13045</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14063</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16042</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14958</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>24640</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>26759</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27652</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>27220</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6930; 17943</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7535; 18756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6634; 17907</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7998; 18816</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8091; 19467</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8651; 20052</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>10556; 23108</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9621; 21908</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>17578; 32689</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>19386; 36163</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20092; 37078</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>20027; 37021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15508</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18869</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24617</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17941</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12442</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19222</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22434</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>32635</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27950</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38091</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>47052</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>50576</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10182; 21653</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13221; 26464</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17980; 32552</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11789; 25535</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7749; 18855</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13526; 26454</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16064; 30726</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>23631; 43146</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20415; 36546</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>29827; 49369</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>37428; 59132</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>40263; 63795</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>50588</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39610</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26962</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25101</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42113</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>43301</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>29285</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>31935</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>92701</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>82910</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56248</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>57036</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>41213; 61684</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31060; 49378</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20547; 35990</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16109; 34597</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>33752; 51616</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>34787; 52625</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>21941; 38358</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>22450; 43752</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>79067; 106635</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>70244; 96949</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>45993; 69831</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>43263; 72019</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>78908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>65539</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59719</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>146507</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>154501</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>134191</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>142515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>65248; 92607</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>61927; 87534</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>53124; 78190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>47668; 74045</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>56136; 80860</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67988; 96061</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>56504; 83849</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>67496; 98738</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>126605; 165722</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>134359; 174051</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>116934; 152569</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>124334; 166277</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP26C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,87</t>
+          <t>0,46; 4,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,31</t>
+          <t>0,52; 4,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 14,58</t>
+          <t>3,69; 14,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,03</t>
+          <t>1,38; 6,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,91</t>
+          <t>2,81; 11,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,24</t>
+          <t>1,22; 4,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,01</t>
+          <t>0,48; 3,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 10,09</t>
+          <t>4,04; 10,47</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,09</t>
+          <t>2,97; 7,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,02</t>
+          <t>3,36; 8,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,56</t>
+          <t>3,5; 8,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,81</t>
+          <t>4,75; 11,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,69</t>
+          <t>3,15; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,51</t>
+          <t>3,39; 7,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,95</t>
+          <t>4,06; 9,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,0</t>
+          <t>5,21; 12,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,46</t>
+          <t>3,51; 6,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,22</t>
+          <t>3,84; 7,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,93</t>
+          <t>4,21; 7,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,83</t>
+          <t>5,75; 10,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,98; 16,98</t>
+          <t>8,21; 17,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,42; 16,85</t>
+          <t>8,17; 16,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,55; 17,29</t>
+          <t>9,5; 17,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,75</t>
+          <t>7,29; 15,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 13,39</t>
+          <t>5,54; 13,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 16,68</t>
+          <t>8,21; 16,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 16,29</t>
+          <t>8,64; 16,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,12; 20,31</t>
+          <t>11,04; 20,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,62</t>
+          <t>7,84; 13,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 15,64</t>
+          <t>9,23; 15,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 15,69</t>
+          <t>9,78; 15,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,44; 16,55</t>
+          <t>10,09; 16,58</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 31,78</t>
+          <t>21,54; 31,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 29,03</t>
+          <t>18,2; 29,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 20,77</t>
+          <t>11,54; 20,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 12,61</t>
+          <t>6,05; 12,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,55; 25,3</t>
+          <t>16,66; 25,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 29,61</t>
+          <t>19,25; 30,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 22,12</t>
+          <t>12,22; 21,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 14,32</t>
+          <t>7,26; 13,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,86; 26,79</t>
+          <t>20,04; 26,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,2; 27,88</t>
+          <t>20,21; 27,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 20,14</t>
+          <t>13,07; 19,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,42</t>
+          <t>7,76; 12,7</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,64</t>
+          <t>9,67; 13,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,44</t>
+          <t>8,77; 12,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,22</t>
+          <t>7,7; 11,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,15</t>
+          <t>7,17; 11,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,28</t>
+          <t>7,73; 11,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,89</t>
+          <t>9,14; 12,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,35</t>
+          <t>7,51; 11,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,97</t>
+          <t>8,8; 13,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,87</t>
+          <t>9,09; 11,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,02</t>
+          <t>9,36; 12,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,63</t>
+          <t>8,16; 10,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,66</t>
+          <t>8,67; 11,63</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4448</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>648; 5521</t>
+          <t>652; 6029</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>566; 5436</t>
+          <t>653; 5656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2200; 8383</t>
+          <t>2122; 8402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2049; 9965</t>
+          <t>1951; 8660</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4398</t>
+          <t>0; 5314</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1550; 6657</t>
+          <t>1714; 6749</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4395</t>
+          <t>0; 4296</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3390; 12058</t>
+          <t>3465; 12395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1229; 7359</t>
+          <t>1185; 7577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4624; 11965</t>
+          <t>4789; 12413</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6930; 17943</t>
+          <t>7510; 18308</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7535; 18756</t>
+          <t>7869; 19755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6634; 17907</t>
+          <t>7325; 17956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7998; 18816</t>
+          <t>7564; 19037</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8091; 19467</t>
+          <t>7980; 19188</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8651; 20052</t>
+          <t>9038; 20582</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10556; 23108</t>
+          <t>10476; 23463</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9621; 21908</t>
+          <t>9503; 22500</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17578; 32689</t>
+          <t>17764; 32964</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19386; 36163</t>
+          <t>19250; 35934</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20092; 37078</t>
+          <t>19698; 36209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20027; 37021</t>
+          <t>19669; 35169</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10182; 21653</t>
+          <t>10467; 22323</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13221; 26464</t>
+          <t>12838; 26598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17980; 32552</t>
+          <t>17892; 33110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11789; 25535</t>
+          <t>12620; 26046</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7749; 18855</t>
+          <t>7808; 18726</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13526; 26454</t>
+          <t>13016; 26340</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16064; 30726</t>
+          <t>16291; 30665</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23631; 43146</t>
+          <t>23456; 43601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20415; 36546</t>
+          <t>21029; 36837</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29827; 49369</t>
+          <t>29137; 47803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37428; 59132</t>
+          <t>36857; 58615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40263; 63795</t>
+          <t>38897; 63919</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41213; 61684</t>
+          <t>41809; 61423</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31060; 49378</t>
+          <t>30959; 49979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20547; 35990</t>
+          <t>19993; 35343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16109; 34597</t>
+          <t>16595; 34763</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33752; 51616</t>
+          <t>33980; 51827</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34787; 52625</t>
+          <t>34208; 53825</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21941; 38358</t>
+          <t>21186; 37300</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22450; 43752</t>
+          <t>22172; 42650</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79067; 106635</t>
+          <t>79774; 107137</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70244; 96949</t>
+          <t>70285; 96048</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45993; 69831</t>
+          <t>45311; 69202</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43263; 72019</t>
+          <t>44960; 73628</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65248; 92607</t>
+          <t>65682; 92845</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61927; 87534</t>
+          <t>61693; 87705</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53124; 78190</t>
+          <t>53642; 78767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47668; 74045</t>
+          <t>47650; 73478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56136; 80860</t>
+          <t>55401; 82080</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67988; 96061</t>
+          <t>68057; 96554</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56504; 83849</t>
+          <t>55483; 82556</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67496; 98738</t>
+          <t>67044; 99187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>126605; 165722</t>
+          <t>126903; 164698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134359; 174051</t>
+          <t>135645; 174286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116934; 152569</t>
+          <t>117201; 152216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>124334; 166277</t>
+          <t>123542; 165872</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP26C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,23</t>
+          <t>1,46; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,49</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 14,61</t>
+          <t>2,16; 8,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,11</t>
+          <t>0,45; 3,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,52; 4,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,06</t>
+          <t>3,36; 13,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,36</t>
+          <t>1,2; 4,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,1</t>
+          <t>0,5; 2,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,47</t>
+          <t>3,42; 9,54</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,55%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,23</t>
+          <t>3,37; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,44</t>
+          <t>3,36; 8,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,58</t>
+          <t>4,06; 9,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,95</t>
+          <t>5,28; 12,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,58</t>
+          <t>2,74; 7,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,71</t>
+          <t>3,23; 8,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,09</t>
+          <t>3,39; 8,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,33</t>
+          <t>5,53; 12,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,51</t>
+          <t>3,51; 6,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,17</t>
+          <t>3,9; 7,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,75</t>
+          <t>4,2; 7,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,29</t>
+          <t>6,02; 11,13</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,02%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13,08%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,5</t>
+          <t>5,61; 13,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 16,94</t>
+          <t>8,36; 17,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 17,59</t>
+          <t>8,54; 16,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 15,05</t>
+          <t>11,7; 21,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 13,3</t>
+          <t>8,04; 17,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 16,61</t>
+          <t>8,42; 17,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 16,26</t>
+          <t>9,54; 17,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,04; 20,52</t>
+          <t>7,01; 14,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 13,73</t>
+          <t>7,85; 13,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,15</t>
+          <t>9,51; 15,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,55</t>
+          <t>9,87; 15,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 16,58</t>
+          <t>10,35; 16,77</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26,06%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23,29%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>15,56%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 31,65</t>
+          <t>16,18; 24,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 29,39</t>
+          <t>19,17; 29,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,39</t>
+          <t>12,74; 22,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 12,67</t>
+          <t>7,61; 14,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 25,41</t>
+          <t>21,24; 31,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,25; 30,29</t>
+          <t>18,08; 29,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 21,51</t>
+          <t>11,4; 20,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,96</t>
+          <t>7,04; 13,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,04; 26,91</t>
+          <t>19,81; 26,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 27,62</t>
+          <t>19,72; 27,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,96</t>
+          <t>13,11; 19,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,7</t>
+          <t>8,71; 13,38</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,67</t>
+          <t>7,78; 11,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,47</t>
+          <t>9,18; 12,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,3</t>
+          <t>7,64; 11,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,06</t>
+          <t>9,13; 13,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,45</t>
+          <t>9,7; 13,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,96</t>
+          <t>8,56; 12,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,18</t>
+          <t>7,59; 11,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,02</t>
+          <t>7,78; 11,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,8</t>
+          <t>9,31; 11,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,03</t>
+          <t>9,41; 12,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,6</t>
+          <t>8,16; 10,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,63</t>
+          <t>9,2; 12,14</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2334</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1216</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2044</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2349</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4415</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4698</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>6051</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4235</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>652; 6029</t>
+          <t>2068; 9669</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>653; 5656</t>
+          <t>0; 4895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2122; 8402</t>
+          <t>1083; 4408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4148</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1951; 8660</t>
+          <t>648; 5507</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5314</t>
+          <t>659; 6166</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1714; 6749</t>
+          <t>1753; 7237</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>0; 3975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3465; 12395</t>
+          <t>3400; 12750</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1185; 7577</t>
+          <t>1225; 7183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4789; 12413</t>
+          <t>3496; 9755</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13045</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14063</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16042</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13024</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11595</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12696</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11610</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12262</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13045</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14063</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16042</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>25373</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7510; 18308</t>
+          <t>8536; 20537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7869; 19755</t>
+          <t>8960; 21364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7325; 17956</t>
+          <t>10478; 23625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7564; 19037</t>
+          <t>8313; 19595</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7980; 19188</t>
+          <t>6949; 17854</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9038; 20582</t>
+          <t>7553; 19153</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10476; 23463</t>
+          <t>7093; 17981</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9503; 22500</t>
+          <t>8044; 18816</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17764; 32964</t>
+          <t>17751; 32863</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19250; 35934</t>
+          <t>19514; 35660</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19698; 36209</t>
+          <t>19612; 36661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19669; 35169</t>
+          <t>18238; 33723</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12442</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19222</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22434</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15508</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>18869</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>24617</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12442</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19222</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22434</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32635</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50576</t>
+          <t>49996</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10467; 22323</t>
+          <t>7897; 18735</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12838; 26598</t>
+          <t>13250; 27162</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17892; 33110</t>
+          <t>16108; 31282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12620; 26046</t>
+          <t>23415; 43019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7808; 18726</t>
+          <t>10250; 21976</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13016; 26340</t>
+          <t>13218; 26984</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16291; 30665</t>
+          <t>17954; 33058</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23456; 43601</t>
+          <t>12244; 25550</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21029; 36837</t>
+          <t>21060; 36832</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29137; 47803</t>
+          <t>30010; 49143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36857; 58615</t>
+          <t>37200; 58623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38897; 63919</t>
+          <t>38779; 62856</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42113</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>43301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29285</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31916</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50588</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>39610</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26962</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25101</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42113</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43301</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>29285</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>58472</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41809; 61423</t>
+          <t>32994; 50942</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30959; 49979</t>
+          <t>34073; 52923</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19993; 35343</t>
+          <t>22082; 38161</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16595; 34763</t>
+          <t>22281; 42193</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33980; 51827</t>
+          <t>41223; 61218</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34208; 53825</t>
+          <t>30758; 49406</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21186; 37300</t>
+          <t>19757; 35581</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22172; 42650</t>
+          <t>17963; 34638</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79774; 107137</t>
+          <t>78875; 105525</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70285; 96048</t>
+          <t>68591; 95390</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45311; 69202</t>
+          <t>45441; 67788</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44960; 73628</t>
+          <t>47720; 73339</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65682; 92845</t>
+          <t>55776; 80366</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61693; 87705</t>
+          <t>68407; 96745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53642; 78767</t>
+          <t>56425; 82320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47650; 73478</t>
+          <t>63956; 94496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55401; 82080</t>
+          <t>65895; 93971</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68057; 96554</t>
+          <t>60202; 86826</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55483; 82556</t>
+          <t>52926; 78613</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67044; 99187</t>
+          <t>48839; 73096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>126903; 164698</t>
+          <t>129891; 164954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135645; 174286</t>
+          <t>136374; 174848</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117201; 152216</t>
+          <t>117083; 153372</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>123542; 165872</t>
+          <t>122247; 161261</t>
         </is>
       </c>
     </row>
